--- a/tests/testdata/excel/シート名記号.xlsx
+++ b/tests/testdata/excel/シート名記号.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AD65D91-64D9-44A4-9E69-54D765FE1104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{939DFB39-72D2-4C58-BEA0-1176E32683B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{09EB8017-4B62-4A68-AEE7-7D64EB3D60F9}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{4556608E-B350-43F3-B8CC-E2839D7A2C82}"/>
   </bookViews>
   <sheets>
     <sheet name="不等号&lt;&gt;" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,8 @@
     <sheet name="1234567890123456789012345678901" sheetId="10" r:id="rId10"/>
     <sheet name="衝突&quot;" sheetId="11" r:id="rId11"/>
     <sheet name="衝突”" sheetId="12" r:id="rId12"/>
+    <sheet name="タブ_x0009_あり" sheetId="13" r:id="rId13"/>
+    <sheet name="改行_x000a_あり" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>TC09-01</t>
   </si>
@@ -122,6 +124,19 @@
   </si>
   <si>
     <t>シート名: 衝突”</t>
+  </si>
+  <si>
+    <t>TC09-13</t>
+  </si>
+  <si>
+    <t>シート名: タブ	あり</t>
+  </si>
+  <si>
+    <t>TC09-14</t>
+  </si>
+  <si>
+    <t>シート名: 改行
+あり</t>
   </si>
 </sst>
 </file>
@@ -167,9 +182,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +522,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66125537-6A48-4B17-B9DD-16D5D5D835B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A05EDE8-B19D-4EC6-8FCF-52178019906E}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -523,7 +541,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A46FD17F-852E-4CD2-B173-908F473FF81A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F2282D-485D-45CE-BD63-08E7C0F885F7}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -542,7 +560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9357565-C503-494C-B7B7-2F53FAEDB262}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3D40809-9369-43F0-99CC-034F415D601D}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -561,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C10C1C5C-8662-4F5A-BDDF-BBEA0678476E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC27E1BD-8FC1-4BDF-92B7-E5754ECC0067}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -579,8 +597,46 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97215B91-8CF6-4102-9981-F033CABD1DF4}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9F2EB2-5F0D-456A-92EA-E230DAD2CF57}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E2E06B-1B0B-42C7-B918-786C7B836DC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9FC07ED-644D-4DC1-8AEC-E2FA99B8A0B0}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -599,7 +655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0300F014-1225-4EBF-82F0-D0FE70855B61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ACCDE1F-E7CF-4944-8C6D-A755EA307E36}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -618,7 +674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8295CC06-3C7C-4514-91DF-62D2471AC0B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905EAD3F-3A85-4D99-8AE4-2A5924BF2570}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -637,7 +693,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{454E318D-E47B-4636-BC7D-2A1CBEDBE757}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{743C7FDA-A57B-4F43-AA4A-5CA1D2B13143}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -656,7 +712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3688D8B-A907-4944-8057-CA61430D102A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C69CD0-CA5D-47EE-940C-29BDEDA70E8F}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -675,7 +731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DB162D5-558C-433A-A3DB-1A766B0B3C9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11168B28-ACAC-439D-BBF1-2E677E0CAF86}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -694,7 +750,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E0E302-234D-409F-99DE-D0774E5189B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12E0CA93-8376-475E-94D0-32C940504F06}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -713,7 +769,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFDFDD7D-42A4-4BE6-B29A-20F911021A88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8446DE1-9732-42A3-9212-BC2BB7F6EDEB}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/シート名記号.xlsx
+++ b/tests/testdata/excel/シート名記号.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{939DFB39-72D2-4C58-BEA0-1176E32683B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{707625D2-81CF-4B53-B1B1-04F76B49A578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{4556608E-B350-43F3-B8CC-E2839D7A2C82}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{AF3F5E49-FC53-466C-923A-F68D20DAE9A9}"/>
   </bookViews>
   <sheets>
     <sheet name="不等号&lt;&gt;" sheetId="1" r:id="rId1"/>
@@ -522,7 +522,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A05EDE8-B19D-4EC6-8FCF-52178019906E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB1A92B-73F2-43E7-9A54-AF76EF66C685}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -541,7 +541,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F2282D-485D-45CE-BD63-08E7C0F885F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B24ABEA-7C44-4493-A49E-6FA448D8799F}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -560,7 +560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3D40809-9369-43F0-99CC-034F415D601D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2860595-120B-491C-8B6D-166655A7D42C}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -579,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC27E1BD-8FC1-4BDF-92B7-E5754ECC0067}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6606AC3-6E9D-46FF-B002-69F12D2E3720}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -598,7 +598,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97215B91-8CF6-4102-9981-F033CABD1DF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF32690F-538B-49E7-9A29-AAE636D9F29D}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -617,7 +617,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9F2EB2-5F0D-456A-92EA-E230DAD2CF57}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC242396-11CD-41ED-A993-3B40CA23E4CF}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -636,7 +636,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9FC07ED-644D-4DC1-8AEC-E2FA99B8A0B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{545A9152-9A6F-495B-83BD-DA14E3E9DC21}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -655,7 +655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ACCDE1F-E7CF-4944-8C6D-A755EA307E36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E9C8EEB-C20B-46E0-968B-AF0EAD793698}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -674,7 +674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905EAD3F-3A85-4D99-8AE4-2A5924BF2570}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{973BFB99-2D29-48DE-982A-CD2D8EE5BF8F}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -693,7 +693,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{743C7FDA-A57B-4F43-AA4A-5CA1D2B13143}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0021036D-2C4F-4E94-B4B1-3014D21A3D1A}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -712,7 +712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C69CD0-CA5D-47EE-940C-29BDEDA70E8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB3C37FE-28F9-46AA-99BE-81985E9F9E3D}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -731,7 +731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11168B28-ACAC-439D-BBF1-2E677E0CAF86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C8D6F9-DB49-4ED3-8A7D-8554FD6EABE6}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -750,7 +750,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12E0CA93-8376-475E-94D0-32C940504F06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42A14ADC-DAE2-46F3-B198-6042C0FF54BE}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -769,7 +769,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8446DE1-9732-42A3-9212-BC2BB7F6EDEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1E43E7E-7140-4D83-9DAF-83B0402D9ADF}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
